--- a/output/pdf_financials_xlsx/XRTX.xlsx
+++ b/output/pdf_financials_xlsx/XRTX.xlsx
@@ -4333,13 +4333,13 @@
         <v>0.1962</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.264578</v>
+        <v>0.354812</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.279649</v>
+        <v>0.296535</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.5814859999999999</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -4353,16 +4353,16 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.991594</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.468257</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.039078</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.778074</v>
       </c>
     </row>
     <row r="93">
@@ -7159,7 +7159,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -8960,7 +8964,11 @@
           <t>Reserves 12 5,468,257 6,197,158</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12177,7 +12185,11 @@
           <t>Share-based payments and warrants reserve</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -13627,7 +13639,11 @@
           <t>Share-based Payments Reserve</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XRTX.xlsx
+++ b/output/pdf_financials_xlsx/XRTX.xlsx
@@ -886,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.103589</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.253543</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.121908</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1558,13 +1558,13 @@
         <v>-1.579274</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.718882</v>
+        <v>-7.822471</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.158065</v>
+        <v>-2.411608</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.313346</v>
+        <v>-3.435254</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1642,13 +1642,13 @@
         <v>-1.579274</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.718882</v>
+        <v>-7.822471</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.158065</v>
+        <v>-2.411608</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.313346</v>
+        <v>-3.435254</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -1836,19 +1836,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000762</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.016769</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.061939</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.260019</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.058614</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -1859,16 +1859,16 @@
         <v>18.851244</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>14.125522</v>
+        <v>14.869861</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.447665</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.473649</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.864514</v>
       </c>
     </row>
     <row r="35">
@@ -1920,19 +1920,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000762</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.016769</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.061939</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.260019</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.058614</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -1943,16 +1943,16 @@
         <v>18.851244</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>14.125522</v>
+        <v>14.869861</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.447665</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.473649</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.864514</v>
       </c>
     </row>
     <row r="37">
@@ -2424,19 +2424,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.000762</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.016417</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.06354700000000001</v>
+        <v>0.001608</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.979648</v>
+        <v>0.719629</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.815248</v>
+        <v>0.756634</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -2447,16 +2447,16 @@
         <v>1.270556</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.746554</v>
+        <v>1.002215</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>4.008072</v>
+        <v>0.560407</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.659061</v>
+        <v>0.185412</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.180926</v>
+        <v>0.316412</v>
       </c>
     </row>
     <row r="49">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">

--- a/output/pdf_financials_xlsx/XRTX.xlsx
+++ b/output/pdf_financials_xlsx/XRTX.xlsx
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>4.9e-05</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -1597,16 +1597,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.014266</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.017077</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.066632</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.03107</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>-0.414834</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.474201</v>
+        <v>-0.474152</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.775923</v>
@@ -1639,16 +1639,16 @@
         <v>-1.284602</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.579274</v>
+        <v>-1.565008</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.822471</v>
+        <v>-7.805394</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.411608</v>
+        <v>-2.344976</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.435254</v>
+        <v>-3.404184</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>4.9e-05</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -20740,7 +20740,11 @@
           <t>Amortization of tangible assets</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -28116,7 +28120,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -30407,7 +30411,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">

--- a/output/pdf_financials_xlsx/XRTX.xlsx
+++ b/output/pdf_financials_xlsx/XRTX.xlsx
@@ -673,16 +673,16 @@
         <v>0.249637</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.413928</v>
+        <v>0.463294</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.950962</v>
+        <v>1.073534</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.089677</v>
+        <v>1.269083</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.392086</v>
+        <v>1.560229</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -799,16 +799,16 @@
         <v>0.629972</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.815776</v>
+        <v>1.865142</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8.021936</v>
+        <v>8.144508</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.508392</v>
+        <v>3.687798</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.575916</v>
+        <v>1.744059</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -3126,33 +3126,31 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.416683</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.414738</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.607389</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.389982</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.410701</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.758486</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.195814</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.08402</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.395539</v>
       </c>
     </row>
     <row r="65">
@@ -3249,36 +3247,34 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.215029</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.383394</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.544086</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.644231</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.290298</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.202259</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.087614</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.06318500000000001</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.158245</v>
       </c>
     </row>
     <row r="68">
@@ -5037,16 +5033,16 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.005376</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.001921</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.001638</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.000846</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
@@ -5077,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00117</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -5092,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019696</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004311</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -5274,34 +5270,34 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.02456</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.011314</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.041073</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.01435</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.031807</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.026005</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.042052</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.038924</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.055223</v>
       </c>
     </row>
     <row r="117">
@@ -6019,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00117</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -6034,10 +6030,10 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019696</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004311</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -6059,7 +6055,7 @@
         <v>-0.174233</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.186425</v>
+        <v>-0.187595</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.555357</v>
@@ -6074,10 +6070,10 @@
         <v>-4.605182</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-8.302104999999999</v>
+        <v>-8.321801000000001</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-6.579124</v>
+        <v>-6.583435</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-3.714601</v>
@@ -8522,7 +8518,11 @@
           <t>Current portion of lease obligation 11 11,510 66,090</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -15527,7 +15527,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -15584,7 +15588,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -17261,7 +17269,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -18322,7 +18334,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -20959,7 +20975,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -21028,7 +21048,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -22687,7 +22711,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E236" s="5" t="n">
         <v>0.1045</v>
       </c>
@@ -27675,7 +27703,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -32576,7 +32608,11 @@
           <t>Directors’ fees 14</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
